--- a/data/trans_dic/P15D$consultar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,51</t>
+          <t>0,0; 49,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 30,6</t>
+          <t>4,76; 32,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,3; 71,64</t>
+          <t>24,22; 68,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,29</t>
+          <t>0,0; 70,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 25,23</t>
+          <t>2,82; 24,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 17,0</t>
+          <t>1,86; 16,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 44,79</t>
+          <t>5,28; 42,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 18,59</t>
+          <t>2,25; 18,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 37,89</t>
+          <t>13,02; 36,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,99</t>
+          <t>1,26; 9,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,8</t>
+          <t>0,0; 57,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 19,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 43,66</t>
+          <t>3,84; 47,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,09</t>
+          <t>0,0; 25,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,02; 51,92</t>
+          <t>21,55; 49,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,99</t>
+          <t>0,0; 26,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 15,26</t>
+          <t>1,62; 16,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 41,07</t>
+          <t>17,75; 40,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,81</t>
+          <t>0,0; 29,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,89</t>
+          <t>1,76; 16,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 38,37</t>
+          <t>7,4; 38,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 26,12</t>
+          <t>2,32; 27,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 25,75</t>
+          <t>4,9; 25,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 55,24</t>
+          <t>6,79; 53,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 41,23</t>
+          <t>9,96; 41,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,45</t>
+          <t>0,0; 27,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 17,85</t>
+          <t>4,16; 17,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 38,55</t>
+          <t>10,65; 37,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 28,44</t>
+          <t>8,41; 29,98</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,12</t>
+          <t>0,0; 38,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,97</t>
+          <t>0,0; 21,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 24,16</t>
+          <t>2,55; 23,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,44</t>
+          <t>0,0; 25,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,58</t>
+          <t>0,0; 41,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 17,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 33,33</t>
+          <t>3,23; 33,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 27,8</t>
+          <t>3,3; 25,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 15,45</t>
+          <t>3,61; 16,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 20,32</t>
+          <t>2,4; 18,8</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 76,42</t>
+          <t>12,25; 81,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,91</t>
+          <t>0,0; 34,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,62</t>
+          <t>0,0; 53,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,86</t>
+          <t>0,0; 68,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,19</t>
+          <t>0,0; 39,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 62,5</t>
+          <t>10,83; 62,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 28,2</t>
+          <t>2,84; 31,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,47</t>
+          <t>0,0; 37,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,25</t>
+          <t>0,0; 18,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 28,76</t>
+          <t>3,07; 25,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 26,06</t>
+          <t>4,62; 25,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 25,52</t>
+          <t>2,77; 24,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 27,5</t>
+          <t>3,43; 26,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 31,81</t>
+          <t>10,86; 32,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 15,93</t>
+          <t>2,88; 15,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,72; 22,47</t>
+          <t>5,83; 22,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,41; 24,97</t>
+          <t>10,65; 25,45</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 42,69</t>
+          <t>7,15; 39,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 21,53</t>
+          <t>6,02; 22,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 31,94</t>
+          <t>5,31; 31,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,41</t>
+          <t>0,0; 32,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 23,65</t>
+          <t>5,01; 22,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,06</t>
+          <t>0,0; 25,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 28,32</t>
+          <t>9,11; 27,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 30,44</t>
+          <t>7,35; 30,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 19,46</t>
+          <t>7,1; 19,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,02</t>
+          <t>0,0; 15,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 25,62</t>
+          <t>9,77; 24,89</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,22</t>
+          <t>0,0; 23,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 23,45</t>
+          <t>2,61; 21,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,62; 39,62</t>
+          <t>7,72; 39,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,53</t>
+          <t>0,0; 22,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 30,37</t>
+          <t>3,59; 32,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 26,47</t>
+          <t>4,54; 27,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 26,04</t>
+          <t>5,8; 24,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,36</t>
+          <t>0,0; 11,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 21,37</t>
+          <t>4,76; 21,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 14,23</t>
+          <t>2,51; 14,63</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,55</t>
+          <t>8,14; 20,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,82</t>
+          <t>5,15; 11,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,12</t>
+          <t>8,8; 18,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 14,18</t>
+          <t>5,2; 14,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,56</t>
+          <t>7,27; 21,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,97</t>
+          <t>5,32; 12,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,18</t>
+          <t>6,63; 15,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,27; 23,35</t>
+          <t>14,49; 23,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,71</t>
+          <t>8,86; 18,51</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,4</t>
+          <t>6,03; 11,18</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,16</t>
+          <t>8,61; 14,69</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,44</t>
+          <t>11,09; 17,28</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1736; 11332</t>
+          <t>1763; 12109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4859; 13760</t>
+          <t>4652; 13208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1161</t>
+          <t>0; 1328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4982</t>
+          <t>0; 4975</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>922; 7616</t>
+          <t>852; 7322</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>540; 4927</t>
+          <t>538; 4919</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>921; 7336</t>
+          <t>866; 6973</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1356; 12022</t>
+          <t>1452; 12113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6592; 18717</t>
+          <t>6431; 18144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>673; 5701</t>
+          <t>718; 5502</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 4540</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6086</t>
+          <t>0; 6177</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>984; 10627</t>
+          <t>935; 11535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1680</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6682</t>
+          <t>0; 7567</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7346; 17323</t>
+          <t>7191; 16675</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4369</t>
+          <t>0; 4524</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1037; 9361</t>
+          <t>993; 9899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9805; 23698</t>
+          <t>10244; 23248</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6528</t>
+          <t>0; 5443</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>949; 8927</t>
+          <t>932; 8827</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1708; 8914</t>
+          <t>1719; 9027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>464; 5572</t>
+          <t>495; 5805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1524</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1925; 10259</t>
+          <t>1950; 10305</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>964; 7667</t>
+          <t>943; 7438</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3174; 11048</t>
+          <t>2670; 11088</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6383</t>
+          <t>0; 6230</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4803; 16543</t>
+          <t>3856; 15766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3816; 14305</t>
+          <t>3951; 13886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4147; 13686</t>
+          <t>4046; 14431</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6079</t>
+          <t>0; 6844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6397</t>
+          <t>0; 6498</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1019; 9275</t>
+          <t>981; 8998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4855</t>
+          <t>0; 6063</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4071</t>
+          <t>0; 4054</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1830</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6948</t>
+          <t>0; 6499</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>592; 6069</t>
+          <t>588; 6093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>899; 7676</t>
+          <t>911; 6905</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 7348</t>
+          <t>0; 6295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2700; 11551</t>
+          <t>2702; 12236</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1039; 8527</t>
+          <t>1007; 7888</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>843; 5593</t>
+          <t>897; 5937</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5521</t>
+          <t>0; 4501</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4618</t>
+          <t>0; 5407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1333</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5375</t>
+          <t>0; 5378</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7956</t>
+          <t>0; 7878</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1486</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 417</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1085; 9453</t>
+          <t>1638; 9384</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>922; 9298</t>
+          <t>936; 10220</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5451</t>
+          <t>0; 5040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 1307</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1845</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4931</t>
+          <t>0; 5670</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>868; 8117</t>
+          <t>867; 7315</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1298; 6783</t>
+          <t>1204; 6541</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1811</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>982; 9039</t>
+          <t>979; 8768</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1060; 10026</t>
+          <t>1251; 9656</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3240; 8587</t>
+          <t>2933; 8790</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1922; 10479</t>
+          <t>1891; 10292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3701; 14536</t>
+          <t>3772; 14466</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5519; 13239</t>
+          <t>5649; 13497</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2000; 11648</t>
+          <t>1951; 10880</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3817; 13944</t>
+          <t>3898; 14750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1990; 13877</t>
+          <t>2306; 13828</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5969</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3238; 14112</t>
+          <t>2989; 13264</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6047</t>
+          <t>0; 7017</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4722; 14188</t>
+          <t>4563; 13877</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3508; 13911</t>
+          <t>3358; 14154</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9110; 24212</t>
+          <t>8831; 23992</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 8087</t>
+          <t>0; 8124</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9234; 23970</t>
+          <t>9142; 23286</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6919</t>
+          <t>0; 6213</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908; 8117</t>
+          <t>904; 7414</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2052; 10670</t>
+          <t>2079; 10654</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 6715</t>
+          <t>0; 5569</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>955; 8119</t>
+          <t>960; 8763</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1418; 7575</t>
+          <t>1298; 7873</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3255; 13885</t>
+          <t>3092; 13084</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 5605</t>
+          <t>0; 5639</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2850; 13110</t>
+          <t>2920; 12959</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1222; 7764</t>
+          <t>1370; 7984</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10210; 25289</t>
+          <t>10013; 24879</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15411; 33541</t>
+          <t>14609; 33785</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16848; 36178</t>
+          <t>17558; 36131</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10158; 28360</t>
+          <t>10397; 29251</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6496; 21166</t>
+          <t>6823; 20507</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13931; 32991</t>
+          <t>13536; 31420</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11817; 28885</t>
+          <t>12618; 29936</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30477; 49877</t>
+          <t>30958; 51066</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19934; 40590</t>
+          <t>19210; 40138</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33805; 61371</t>
+          <t>32422; 60169</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33298; 59107</t>
+          <t>33563; 57282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>44914; 72141</t>
+          <t>45885; 71479</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$consultar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,91</t>
+          <t>0,0; 41,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 32,69</t>
+          <t>3,5; 32,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,22; 68,77</t>
+          <t>23,79; 67,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 19,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,19</t>
+          <t>0,0; 78,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 24,26</t>
+          <t>2,93; 25,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 16,98</t>
+          <t>1,63; 15,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 42,57</t>
+          <t>5,73; 50,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 18,73</t>
+          <t>2,09; 18,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,02; 36,73</t>
+          <t>13,13; 37,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 9,64</t>
+          <t>2,02; 12,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,82</t>
+          <t>0,0; 58,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,88</t>
+          <t>0,0; 19,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 47,38</t>
+          <t>4,24; 44,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,01</t>
+          <t>0,0; 21,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 49,98</t>
+          <t>22,13; 50,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,91</t>
+          <t>0,0; 31,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 16,14</t>
+          <t>1,67; 15,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 40,29</t>
+          <t>17,63; 40,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,86</t>
+          <t>0,0; 32,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 16,7</t>
+          <t>1,77; 15,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 38,86</t>
+          <t>7,63; 40,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 27,21</t>
+          <t>2,27; 24,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 25,87</t>
+          <t>4,77; 27,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 53,58</t>
+          <t>7,32; 57,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 41,38</t>
+          <t>10,51; 40,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,77</t>
+          <t>0,0; 29,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 17,01</t>
+          <t>4,26; 16,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,65; 37,42</t>
+          <t>12,21; 36,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 29,98</t>
+          <t>8,61; 28,19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,41</t>
+          <t>0,0; 32,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,31</t>
+          <t>0,0; 18,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 23,44</t>
+          <t>2,49; 23,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,53</t>
+          <t>0,0; 18,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,39</t>
+          <t>0,0; 40,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,87</t>
+          <t>0,0; 18,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 33,46</t>
+          <t>3,22; 33,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 25,01</t>
+          <t>3,34; 27,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 14,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 16,37</t>
+          <t>2,58; 15,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 18,8</t>
+          <t>2,4; 16,83</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 81,11</t>
+          <t>11,9; 86,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,17</t>
+          <t>0,0; 34,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,41</t>
+          <t>0,0; 45,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,89</t>
+          <t>0,0; 68,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,79</t>
+          <t>0,0; 42,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 62,04</t>
+          <t>8,12; 63,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 31,0</t>
+          <t>2,78; 30,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,42</t>
+          <t>0,0; 34,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,68</t>
+          <t>0,0; 20,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 25,92</t>
+          <t>3,16; 28,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 25,12</t>
+          <t>4,61; 24,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 24,76</t>
+          <t>2,8; 24,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 26,49</t>
+          <t>3,38; 27,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 32,56</t>
+          <t>12,73; 33,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 15,65</t>
+          <t>2,98; 16,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 22,36</t>
+          <t>5,79; 21,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,65; 25,45</t>
+          <t>11,02; 25,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 39,88</t>
+          <t>6,5; 40,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 22,77</t>
+          <t>5,71; 22,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 31,83</t>
+          <t>3,86; 26,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,24</t>
+          <t>0,0; 31,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 22,23</t>
+          <t>4,88; 22,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,6</t>
+          <t>0,0; 25,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 27,7</t>
+          <t>8,83; 26,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 30,97</t>
+          <t>6,86; 30,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 19,28</t>
+          <t>7,16; 18,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,09</t>
+          <t>0,0; 13,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,77; 24,89</t>
+          <t>8,59; 23,23</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 22,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 21,43</t>
+          <t>2,63; 21,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 39,56</t>
+          <t>7,91; 40,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,0</t>
+          <t>0,0; 23,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 32,78</t>
+          <t>3,68; 32,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 27,52</t>
+          <t>4,33; 24,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,8; 24,54</t>
+          <t>5,93; 25,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,43</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 21,13</t>
+          <t>4,7; 20,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,63</t>
+          <t>2,23; 14,13</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 20,21</t>
+          <t>7,87; 20,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,91</t>
+          <t>5,12; 11,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,1</t>
+          <t>8,81; 17,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,62</t>
+          <t>5,09; 13,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,27; 21,86</t>
+          <t>6,55; 21,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,35</t>
+          <t>5,49; 12,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,73</t>
+          <t>6,09; 15,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,91</t>
+          <t>14,24; 23,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,51</t>
+          <t>8,81; 17,68</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,18</t>
+          <t>6,21; 11,2</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,69</t>
+          <t>8,6; 15,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,09; 17,28</t>
+          <t>10,64; 16,99</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>3219</t>
         </is>
       </c>
     </row>
@@ -2209,27 +2209,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>0; 3829</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1763; 12109</t>
+          <t>1295; 11895</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4652; 13208</t>
+          <t>4568; 13021</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>0; 5193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4975</t>
+          <t>0; 5555</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,32 +2239,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>852; 7322</t>
+          <t>885; 7758</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>538; 4919</t>
+          <t>496; 4606</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>866; 6973</t>
+          <t>938; 8222</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1452; 12113</t>
+          <t>1351; 11797</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6431; 18144</t>
+          <t>6484; 18377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>718; 5502</t>
+          <t>1161; 7423</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16461</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4540</t>
+          <t>0; 4563</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6177</t>
+          <t>0; 5941</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>935; 11535</t>
+          <t>1046; 10943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7567</t>
+          <t>0; 6484</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7191; 16675</t>
+          <t>7685; 17472</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 5236</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>993; 9899</t>
+          <t>1026; 9389</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10244; 23248</t>
+          <t>10475; 24254</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8089</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5443</t>
+          <t>0; 5997</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>932; 8827</t>
+          <t>935; 8443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1719; 9027</t>
+          <t>1773; 9372</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>495; 5805</t>
+          <t>508; 5430</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1950; 10305</t>
+          <t>1901; 11140</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>943; 7438</t>
+          <t>1016; 7991</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2670; 11088</t>
+          <t>2807; 10732</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6230</t>
+          <t>0; 6544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3856; 15766</t>
+          <t>3953; 15299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3951; 13886</t>
+          <t>4533; 13372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4046; 14431</t>
+          <t>4221; 13819</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3494</t>
         </is>
       </c>
     </row>
@@ -2833,27 +2833,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6844</t>
+          <t>0; 5805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6498</t>
+          <t>0; 5583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>981; 8998</t>
+          <t>954; 8833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6063</t>
+          <t>0; 5056</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4054</t>
+          <t>0; 4005</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,32 +2863,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6499</t>
+          <t>0; 6640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>588; 6093</t>
+          <t>624; 6412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>911; 6905</t>
+          <t>922; 7690</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6295</t>
+          <t>0; 6846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2702; 12236</t>
+          <t>1929; 11501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1007; 7888</t>
+          <t>1141; 7992</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>897; 5937</t>
+          <t>871; 6338</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4501</t>
+          <t>0; 4515</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5407</t>
+          <t>0; 4602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5378</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7878</t>
+          <t>0; 8390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1638; 9384</t>
+          <t>1228; 9580</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>936; 10220</t>
+          <t>917; 9972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9290</t>
         </is>
       </c>
     </row>
@@ -3254,17 +3254,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5670</t>
+          <t>0; 6228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>867; 7315</t>
+          <t>893; 8069</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1204; 6541</t>
+          <t>1199; 6394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,17 +3274,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>979; 8768</t>
+          <t>991; 8681</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1251; 9656</t>
+          <t>1231; 10180</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2933; 8790</t>
+          <t>3581; 9519</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1891; 10292</t>
+          <t>1957; 11070</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3772; 14466</t>
+          <t>3745; 14212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5649; 13497</t>
+          <t>5969; 13819</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>16636</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1951; 10880</t>
+          <t>1773; 10989</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3898; 14750</t>
+          <t>3699; 14435</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,47 +3472,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2306; 13828</t>
+          <t>2155; 14971</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5937</t>
+          <t>0; 5886</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2989; 13264</t>
+          <t>2909; 13355</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 7017</t>
+          <t>0; 6940</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4563; 13877</t>
+          <t>5160; 15728</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3358; 14154</t>
+          <t>3134; 13834</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8831; 23992</t>
+          <t>8908; 23537</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 8124</t>
+          <t>0; 7241</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9142; 23286</t>
+          <t>9807; 26541</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3912</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6213</t>
+          <t>0; 6018</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>904; 7414</t>
+          <t>912; 7425</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,42 +3685,42 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2079; 10654</t>
+          <t>2129; 10901</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5569</t>
+          <t>0; 5825</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>960; 8763</t>
+          <t>985; 8802</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1298; 7873</t>
+          <t>1463; 8174</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3092; 13084</t>
+          <t>3165; 13559</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 5639</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2920; 12959</t>
+          <t>2885; 12429</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1370; 7984</t>
+          <t>1416; 8954</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10013; 24879</t>
+          <t>9685; 25623</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14609; 33785</t>
+          <t>14526; 32864</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17558; 36131</t>
+          <t>17590; 35275</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10397; 29251</t>
+          <t>11255; 30416</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6823; 20507</t>
+          <t>6149; 20042</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13536; 31420</t>
+          <t>13971; 31828</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12618; 29936</t>
+          <t>11592; 29343</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30958; 51066</t>
+          <t>33063; 53568</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19210; 40138</t>
+          <t>19114; 38341</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32422; 60169</t>
+          <t>33423; 60281</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33563; 57282</t>
+          <t>33532; 59360</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>45885; 71479</t>
+          <t>48231; 77018</t>
         </is>
       </c>
     </row>
